--- a/AAII_Financials/Quarterly/PATH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PATH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>PATH</t>
   </si>
@@ -656,404 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>410300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>418400</v>
+      </c>
+      <c r="F8" s="3">
         <v>481100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>411100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>361700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>356600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>423600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>354700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>316300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>335100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>405300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>325900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>287300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>289600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>308500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>262700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>242200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>245100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>289700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>220800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>195500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>186200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>207900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>147300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>139400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>113100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>114800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>83900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>77100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>60300</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>76900</v>
+      </c>
+      <c r="F9" s="3">
         <v>73700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>68700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>64100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>63300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>61900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>63700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>62800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>55100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>53000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>49900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>48700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>43500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>47300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>42800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>44100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>45000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>41200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>43100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>35600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>49000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>20100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>17400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>14700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>13600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>12800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>13700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>13900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>329900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>341500</v>
+      </c>
+      <c r="F10" s="3">
         <v>407400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>342400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>297600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>293300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>361800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>290900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>253500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>280000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>352300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>276000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>238600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>246100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>261200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>219900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>198100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>200100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>248500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>177700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>159900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>137200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>187800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>129900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>124700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>99500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>102000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>70200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>63200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,97 +1110,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>92500</v>
+      </c>
+      <c r="F12" s="3">
         <v>94000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>96500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>97600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>94800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>97400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>96600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>96500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>85000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>84200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>84100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>85900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>74500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>81400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>67300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>67800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>68700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>64400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>61600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>57600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>93000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>29200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>27500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>26500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>26700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>24300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>25800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>32300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1263,62 +1296,68 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>3800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>12600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-9300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-8700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-3200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>10300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>12000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1340,109 +1379,121 @@
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>11500</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F15" s="3">
         <v>2400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>4500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>4200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>3300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>4500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>4600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>4900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>3800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>5400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>5500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>5600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>700</v>
-      </c>
-      <c r="R15" s="3">
-        <v>500</v>
-      </c>
-      <c r="S15" s="3">
-        <v>500</v>
       </c>
       <c r="T15" s="3">
         <v>500</v>
       </c>
       <c r="U15" s="3">
+        <v>500</v>
+      </c>
+      <c r="V15" s="3">
+        <v>500</v>
+      </c>
+      <c r="W15" s="3">
         <v>400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>200</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>373700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>387900</v>
+      </c>
+      <c r="F17" s="3">
         <v>400800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>398000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>380500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>370000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>381000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>395000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>407000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>384600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>390200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>381700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>363200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>335100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>353700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>329700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>362400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>361000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>340600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>337100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>293300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>422200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>193300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>210300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>156400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>158000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>190800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>218400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>227100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>217100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>30400</v>
+      </c>
+      <c r="F18" s="3">
         <v>80300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>13100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-18800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-13400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>42700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-40300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-90700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-49500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>15100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-55800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-75900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-45500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-45200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-67000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-120200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-115900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-50900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-116300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-97800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-236000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>14600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-63000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-44900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-134500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-150000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-156800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,166 +1747,174 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-11500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>19600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-7800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-7700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-13700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-7500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>18200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>10500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-3800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>24100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>39800</v>
+      </c>
+      <c r="F21" s="3">
         <v>82000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>17400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-29700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>47900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-28000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-78400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-43200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>16500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-36700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-62900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-39700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-51600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-112300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-113700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-50700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-115900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-94500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-235100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>10</v>
       </c>
@@ -1860,8 +1933,14 @@
       <c r="AE21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1901,11 +1980,11 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1949,186 +2028,204 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F23" s="3">
         <v>92400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>24600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-19700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>54600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-25500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-82300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-25000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>36600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-27600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-56500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-28300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-56500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-116300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-117800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-54700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-119600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-98300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-238300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>19600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-69200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>7100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-52200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-76200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-132400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-150300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-158200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-12000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-174200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-14800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>3800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>3600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>4800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>8400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>2100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>1900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F26" s="3">
         <v>104500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>198800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-22600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>51800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-10700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-86100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-28700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>33900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-31500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-60400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-31900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-57700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-120400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-122600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-63100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-122800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-100000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-239700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>26300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-70800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>5000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-78100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-133000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-157800</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F27" s="3">
         <v>104500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>198800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-22600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>51800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-10700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-86100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-28700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>33900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-31500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-60400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-31900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-57700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-120400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-122600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-63100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-122800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-100000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-239700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>26300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-70800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>5000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-78100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-133000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-157800</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2883,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>11500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-19600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>7800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>7700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>13700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>7500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-10500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>3800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>6200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-24100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>7300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F33" s="3">
         <v>104500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>198800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-22600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>51800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-10700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-86100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-28700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>33900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-31500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-60400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-31900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-57700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-120400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-122600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-63100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-122800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-100000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-239700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>26300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-70800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>5000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-78100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-133000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-157800</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F35" s="3">
         <v>104500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>198800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-22600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>51800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-10700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-86100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-28700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>33900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-31500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-60400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-31900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-57700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-120400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-122600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-63100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-122800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-100000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-239700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>26300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-70800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>5000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-78100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-133000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-157800</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,77 +3437,79 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>607400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>632200</v>
+      </c>
+      <c r="F41" s="3">
         <v>871200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>743700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>628600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>700600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>879200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>773600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>939300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1146600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1061700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1003100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1093900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1311600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1402100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1451200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1607400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1679200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1768700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1776400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1826400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1796300</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3349,83 +3522,89 @@
       <c r="AC41" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>676600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>675000</v>
+      </c>
+      <c r="F42" s="3">
         <v>601300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>654500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>818900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>854400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>750300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>795400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>804100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>788900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>818100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>814100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>735700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>469100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>354800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>225600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>114200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>114700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>96400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>102000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>70100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>83300</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3438,83 +3617,89 @@
       <c r="AC42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>442300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>410200</v>
+      </c>
+      <c r="F43" s="3">
         <v>580700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>496100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>387200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>369800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>539900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>446100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>368800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>358800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>520500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>457300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>306900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>301800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>443500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>394700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>303100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>266400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>336900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>269400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>198500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>177500</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3527,14 +3712,20 @@
       <c r="AC43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3574,11 +3765,11 @@
       <c r="O44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3622,77 +3813,83 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>147600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>135100</v>
+      </c>
+      <c r="F45" s="3">
         <v>135000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>143700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>138100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>117800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>103400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>101700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>102300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>97800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>91900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>89000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>84200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>97200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>144000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>87800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>83900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>84600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>75300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>59400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>64000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>62900</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3705,83 +3902,89 @@
       <c r="AC45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1926600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1918400</v>
+      </c>
+      <c r="F46" s="3">
         <v>2243900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2093300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2030700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2109700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2338600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2176500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2274300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2469200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2580400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2429700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2303600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2257300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2344400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2159200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2108500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2145000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2277300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2207200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2159100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2119900</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3794,83 +3997,89 @@
       <c r="AC46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>149900</v>
+      </c>
+      <c r="F47" s="3">
         <v>258900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>162400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>115300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>76100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>130400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>72200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>37500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="3">
         <v>5700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>9500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>12400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>8100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>12800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>22300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>14300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>2500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>9100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3883,83 +4092,89 @@
       <c r="AC47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>112000</v>
+      </c>
+      <c r="F48" s="3">
         <v>110500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>109800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>107200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>108300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>99200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>94700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>93100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>83200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>80100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>76200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>77500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>79200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>81100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>78700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>69600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>66700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>66100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>65100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>31000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>31600</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3972,83 +4187,89 @@
       <c r="AC48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>281000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>285800</v>
+      </c>
+      <c r="F49" s="3">
         <v>145300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>142200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>142400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>145400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>95200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>99200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>100600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>101000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>103700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>103800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>109300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>110400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>118500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>115300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>121100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>70000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>73500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>77300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>77300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>82300</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4061,14 +4282,20 @@
       <c r="AC49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,77 +4478,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>30900</v>
+      </c>
+      <c r="F52" s="3">
         <v>11200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>32800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>32100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>34300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>11600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>34100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>36300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>31600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>9500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>26300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>35100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>40700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>181700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>146000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>127400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>130200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>133300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>103700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>78000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>63600</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4328,14 +4567,20 @@
       <c r="AC52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,77 +4668,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2907400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2904700</v>
+      </c>
+      <c r="F54" s="3">
         <v>3179200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2896000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2592300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2644400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2865300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2663300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2701300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2845000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2954800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2787100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2670100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2642700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2735200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2511700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2434700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2424700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2572500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2467700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2347900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2306600</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4506,14 +4757,20 @@
       <c r="AC54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,77 +4837,79 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F57" s="3">
         <v>10200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>19700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>16900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>33200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>18400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>13700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>11300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>12100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>17400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>11500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>23900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4661,14 +4922,20 @@
       <c r="AC57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4676,44 +4943,44 @@
         <v>10300</v>
       </c>
       <c r="E58" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G58" s="3">
         <v>10000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>6700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>13800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>8400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>6900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7300</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4756,77 +5023,83 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>627000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>670300</v>
+      </c>
+      <c r="F59" s="3">
         <v>685100</v>
       </c>
-      <c r="E59" s="3">
-        <v>585300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>587000</v>
-      </c>
       <c r="G59" s="3">
+        <v>598400</v>
+      </c>
+      <c r="H59" s="3">
+        <v>572900</v>
+      </c>
+      <c r="I59" s="3">
         <v>582100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>604800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>522800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>489600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>498300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>531400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>470800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>423400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>420100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>617600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>465400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>448000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>420800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>516000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>443300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>371700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>322900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4839,83 +5112,89 @@
       <c r="AC59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>807300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>831700</v>
+      </c>
+      <c r="F60" s="3">
         <v>905400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>788700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>738400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>715900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>798900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>695500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>632500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>597500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>711700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>627700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>518100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>503400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>626500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>476600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>460100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>438200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>527500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>467300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>374500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>328600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4928,59 +5207,65 @@
       <c r="AC60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>70900</v>
+        <v>69400</v>
       </c>
       <c r="E61" s="3">
         <v>72000</v>
       </c>
       <c r="F61" s="3">
+        <v>70900</v>
+      </c>
+      <c r="G61" s="3">
+        <v>72000</v>
+      </c>
+      <c r="H61" s="3">
         <v>72600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>73400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>74200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>76800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>78200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>62800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>58700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>57700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>56700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>56600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5023,77 +5308,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F62" s="3">
         <v>7000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>11500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>11300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>15500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>6700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>9800</v>
       </c>
       <c r="J62" s="3">
         <v>6700</v>
       </c>
       <c r="K62" s="3">
+        <v>9800</v>
+      </c>
+      <c r="L62" s="3">
         <v>6700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N62" s="3">
         <v>7100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>7900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>8200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>14000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>188600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>175200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>125100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>106300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>123000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>117000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>74400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>78400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5106,14 +5397,20 @@
       <c r="AC62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,77 +5688,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>958800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1001700</v>
+      </c>
+      <c r="F66" s="3">
         <v>1096600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>971400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>926600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>946000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1019500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>931400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>867800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>818000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>938600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>825800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>686800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>687100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>815000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>651900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>585100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>544500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>650500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>584300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>448900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>407000</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5462,14 +5777,20 @@
       <c r="AC66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,77 +6198,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1646900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1683000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1705500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1810000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-2008800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-2010400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1987900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-2039700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-2029000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1942900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1914200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1948100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1916600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1856200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1824300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1796600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1738900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-1618500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-1495900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-1432800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-1210000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5940,14 +6287,20 @@
       <c r="AC72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,77 +6578,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1948600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1903000</v>
+      </c>
+      <c r="F76" s="3">
         <v>2082600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1924600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1665700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1698500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1845800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1731800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1833600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2027000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2016100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1961200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1983400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1955500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1920200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1859800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1849500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1880200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1921900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1883400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1899000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1899500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>10</v>
       </c>
@@ -6296,14 +6667,20 @@
       <c r="AC76" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F81" s="3">
         <v>104500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>198800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-22600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>51800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-10700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-86100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-28700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>33900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-31500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-60400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-31900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-57700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-120400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-122600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-63100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-122800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-100000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-239700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>26300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-70800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>5000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-78100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-133000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-157800</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,77 +7002,79 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F83" s="3">
         <v>500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>2800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>-900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>9700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>3500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>6800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>5400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>5700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>4900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>4000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>4000</v>
       </c>
       <c r="T83" s="3">
         <v>4000</v>
       </c>
       <c r="U83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W83" s="3">
         <v>3700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>3800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>3200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6690,14 +7087,20 @@
       <c r="AC83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,77 +7568,83 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>131900</v>
+      </c>
+      <c r="F89" s="3">
         <v>182300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>28300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>41600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>119000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>146100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>28100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>46400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>100000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>145600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>41900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>44300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>67300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>94000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-27300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-23700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-52900</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-25400</v>
       </c>
       <c r="V89" s="3">
         <v>-6000</v>
       </c>
       <c r="W89" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="X89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-17500</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7224,14 +7657,20 @@
       <c r="AC89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,77 +7702,79 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-12800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-6600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-9700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-3200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-5500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7346,14 +7787,20 @@
       <c r="AC91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,77 +7983,83 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-112800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-42700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>100800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-79900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-16700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-22900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-41700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>35800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-8600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-60300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-235100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-135600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-126500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-118200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-28800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-15700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-6300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-51000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>11000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>10900</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>10</v>
       </c>
@@ -7613,14 +8072,20 @@
       <c r="AC94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7693,11 +8160,11 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,77 +8493,83 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-252200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-14400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-11200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-111600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-235200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-17000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-172600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-215200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-45700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-81900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-69200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-25200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-20600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-6600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-19000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-18200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>20100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>9000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>1442900</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8091,83 +8582,89 @@
       <c r="AC100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-6800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>3100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>3500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-3200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-2700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-2700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>6400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>2300</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>10</v>
       </c>
@@ -8180,83 +8677,89 @@
       <c r="AC101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-237900</v>
+      </c>
+      <c r="F102" s="3">
         <v>127500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>115000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-72000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-178600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>105600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-165700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-207300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>84900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>58600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-90800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-217300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-90500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-156200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-71900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-89500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-7700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-50000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>16700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1438600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>10</v>
       </c>
@@ -8269,10 +8772,16 @@
       <c r="AC102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>
